--- a/artfynd/A 1971-2023 artfynd.xlsx
+++ b/artfynd/A 1971-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1971-2023 artfynd.xlsx
+++ b/artfynd/A 1971-2023 artfynd.xlsx
@@ -1047,7 +1047,7 @@
         <v>121376054</v>
       </c>
       <c r="B5" t="n">
-        <v>108955</v>
+        <v>108965</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1971-2023 artfynd.xlsx
+++ b/artfynd/A 1971-2023 artfynd.xlsx
@@ -1047,7 +1047,7 @@
         <v>121376054</v>
       </c>
       <c r="B5" t="n">
-        <v>108965</v>
+        <v>108978</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1971-2023 artfynd.xlsx
+++ b/artfynd/A 1971-2023 artfynd.xlsx
@@ -1047,7 +1047,7 @@
         <v>121376054</v>
       </c>
       <c r="B5" t="n">
-        <v>108978</v>
+        <v>108979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1971-2023 artfynd.xlsx
+++ b/artfynd/A 1971-2023 artfynd.xlsx
@@ -1047,7 +1047,7 @@
         <v>121376054</v>
       </c>
       <c r="B5" t="n">
-        <v>108979</v>
+        <v>108982</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1971-2023 artfynd.xlsx
+++ b/artfynd/A 1971-2023 artfynd.xlsx
@@ -1047,7 +1047,7 @@
         <v>121376054</v>
       </c>
       <c r="B5" t="n">
-        <v>108982</v>
+        <v>108988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1971-2023 artfynd.xlsx
+++ b/artfynd/A 1971-2023 artfynd.xlsx
@@ -1047,7 +1047,7 @@
         <v>121376054</v>
       </c>
       <c r="B5" t="n">
-        <v>108988</v>
+        <v>108989</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1971-2023 artfynd.xlsx
+++ b/artfynd/A 1971-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55481452</v>
+        <v>55481461</v>
       </c>
       <c r="B2" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703329.9464115505</v>
+        <v>703381</v>
       </c>
       <c r="R2" t="n">
-        <v>6360119.19368915</v>
+        <v>6360089</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,19 +753,9 @@
           <t>2015-10-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55481227</v>
+        <v>55481478</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>2009</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödbrun jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Geastrum rufescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +818,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -848,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703550.7495113668</v>
+        <v>703344</v>
       </c>
       <c r="R3" t="n">
-        <v>6360177.748807786</v>
+        <v>6360065</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,19 +861,9 @@
           <t>2015-10-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,42 +891,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55481890</v>
+        <v>55481452</v>
       </c>
       <c r="B4" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -971,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703313.1601160208</v>
+        <v>703330</v>
       </c>
       <c r="R4" t="n">
-        <v>6360097.275037377</v>
+        <v>6360119</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,22 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,57 +992,62 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Arne Pettersson</t>
+          <t>Arne Pettersson, Dennis Nyström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121376054</v>
+        <v>55481474</v>
       </c>
       <c r="B5" t="n">
-        <v>108997</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2), Gtl</t>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703557</v>
+        <v>703392</v>
       </c>
       <c r="R5" t="n">
-        <v>6360199</v>
+        <v>6360084</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,12 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2015-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,26 +1088,565 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, gles.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Arne Pettersson, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>55481227</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>703551</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6360178</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Arne Pettersson, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>55481219</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>703547</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6360155</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-10-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Arne Pettersson, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121376054</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>703557</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6360199</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, gles.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>106332882</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103691</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222009</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sandviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Viola rupestris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stangsmyr SO, grustagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>703180</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6360108</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1984-01-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1988-12-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Grusgropen S (6410 B) Kvie 1:40. 3 km NNW of the church of Lojsta, near the gravel-pit on open sandy soil.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Grustag, öppen sandig jord.</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>1241433</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Britt Snogerup, Sven Snogerup</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>55481890</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>703313</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6360097</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-10-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1971-2023 artfynd.xlsx
+++ b/artfynd/A 1971-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481461</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481478</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481452</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481474</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481227</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481219</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121376054</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106332882</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,8 +1692,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55481890</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>